--- a/Data/EC/NIT-9018640084.xlsx
+++ b/Data/EC/NIT-9018640084.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA1C5F12-28BB-4AB2-BA2C-D4314AF37D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6553801F-4533-4A56-88F5-5D0B7068D21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{D881DC8B-8C2B-46E3-A989-CD290AB0026B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7539BFDF-9DF8-4E91-B0B4-C148C036EDB7}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -596,22 +596,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11552F69-5059-E452-9F4B-F174A3DEB756}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6185BE09-A1D0-39E0-6DBE-A21B6DF31BF1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -620,7 +620,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -633,7 +633,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -962,23 +962,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{353489A7-879C-45A3-83FC-657D5A227403}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60F67F68-E1BD-4FAE-9A43-2FF579B96734}">
   <dimension ref="B2:J157"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.06640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -991,7 +991,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1002,7 +1002,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1013,7 +1013,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1024,8 +1024,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>54</v>
       </c>
@@ -1040,8 +1040,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1056,8 +1056,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>55</v>
       </c>
@@ -1072,8 +1072,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>56</v>
       </c>
@@ -1092,7 +1092,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1144,7 +1144,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1167,7 +1167,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1190,7 +1190,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1213,7 +1213,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1236,7 +1236,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1259,7 +1259,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1282,7 +1282,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1305,7 +1305,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1328,7 +1328,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1351,7 +1351,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1374,7 +1374,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1397,7 +1397,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1420,7 +1420,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1443,7 +1443,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1466,7 +1466,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1489,7 +1489,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1512,7 +1512,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1535,7 +1535,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1558,7 +1558,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1604,7 +1604,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1627,7 +1627,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1650,7 +1650,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1673,7 +1673,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1696,7 +1696,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1719,7 +1719,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1742,7 +1742,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1765,7 +1765,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1788,7 +1788,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1811,7 +1811,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1834,7 +1834,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1857,7 +1857,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1880,7 +1880,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1903,7 +1903,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1926,7 +1926,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -1949,7 +1949,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -1972,7 +1972,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -1995,7 +1995,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2018,7 +2018,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2041,7 +2041,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2064,7 +2064,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2087,7 +2087,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2110,7 +2110,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2133,7 +2133,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2156,7 +2156,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2179,7 +2179,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2202,7 +2202,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2225,7 +2225,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2248,7 +2248,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2271,7 +2271,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2294,7 +2294,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2317,7 +2317,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2340,7 +2340,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2363,7 +2363,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2386,7 +2386,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2409,7 +2409,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2432,7 +2432,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2455,7 +2455,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2478,7 +2478,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2501,7 +2501,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2524,7 +2524,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2547,7 +2547,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2570,7 +2570,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2593,7 +2593,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2616,7 +2616,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2639,7 +2639,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2662,7 +2662,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2685,7 +2685,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2708,7 +2708,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2731,7 +2731,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2754,7 +2754,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2777,7 +2777,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2800,7 +2800,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2823,7 +2823,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2846,7 +2846,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -2869,7 +2869,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -2892,7 +2892,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -2915,7 +2915,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -2938,7 +2938,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -2961,7 +2961,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -2984,7 +2984,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3007,7 +3007,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3030,7 +3030,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3053,7 +3053,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3076,7 +3076,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3099,7 +3099,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3122,7 +3122,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3145,7 +3145,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3168,7 +3168,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3191,7 +3191,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3214,7 +3214,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3237,7 +3237,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3260,7 +3260,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3283,7 +3283,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3306,7 +3306,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3329,7 +3329,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3352,7 +3352,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3375,7 +3375,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3398,7 +3398,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3421,7 +3421,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3444,7 +3444,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3467,7 +3467,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>44</v>
       </c>
@@ -3490,7 +3490,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>44</v>
       </c>
@@ -3513,7 +3513,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>44</v>
       </c>
@@ -3536,7 +3536,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>44</v>
       </c>
@@ -3559,7 +3559,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>44</v>
       </c>
@@ -3582,7 +3582,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>44</v>
       </c>
@@ -3605,7 +3605,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>44</v>
       </c>
@@ -3628,7 +3628,7 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>44</v>
       </c>
@@ -3651,7 +3651,7 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>44</v>
       </c>
@@ -3674,7 +3674,7 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>44</v>
       </c>
@@ -3697,7 +3697,7 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
@@ -3720,7 +3720,7 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
@@ -3743,7 +3743,7 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
@@ -3766,7 +3766,7 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
@@ -3789,7 +3789,7 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
@@ -3812,7 +3812,7 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
@@ -3835,7 +3835,7 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
@@ -3858,7 +3858,7 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>8</v>
       </c>
@@ -3881,7 +3881,7 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>8</v>
       </c>
@@ -3904,7 +3904,7 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>8</v>
       </c>
@@ -3927,7 +3927,7 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>8</v>
       </c>
@@ -3950,7 +3950,7 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
@@ -3973,7 +3973,7 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
@@ -3996,7 +3996,7 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
@@ -4019,7 +4019,7 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
@@ -4042,7 +4042,7 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="15" t="s">
         <v>8</v>
       </c>
@@ -4065,7 +4065,7 @@
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="15" t="s">
         <v>8</v>
       </c>
@@ -4088,7 +4088,7 @@
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="15" t="s">
         <v>8</v>
       </c>
@@ -4111,7 +4111,7 @@
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="15" t="s">
         <v>8</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="15" t="s">
         <v>8</v>
       </c>
@@ -4157,7 +4157,7 @@
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="15" t="s">
         <v>8</v>
       </c>
@@ -4180,7 +4180,7 @@
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="15" t="s">
         <v>8</v>
       </c>
@@ -4203,7 +4203,7 @@
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" s="15" t="s">
         <v>8</v>
       </c>
@@ -4226,7 +4226,7 @@
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" s="21" t="s">
         <v>8</v>
       </c>
@@ -4249,7 +4249,7 @@
       <c r="I151" s="25"/>
       <c r="J151" s="26"/>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B156" s="32" t="s">
         <v>62</v>
       </c>
@@ -4260,7 +4260,7 @@
       <c r="I156" s="1"/>
       <c r="J156" s="1"/>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B157" s="32" t="s">
         <v>61</v>
       </c>
